--- a/deliverables/exports/track-b/04-icp.xlsx
+++ b/deliverables/exports/track-b/04-icp.xlsx
@@ -478,7 +478,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A26"/>
+  <dimension ref="A1:A31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" min="1" max="1"/>
@@ -522,138 +522,173 @@
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
+          <t>**Reframed after conflict 2.** The two levels now carry a band position from `00-RESOLUTIONS.md`. Buyer maturity was the right axis. The bands make it measurable, because they describe what the member's setup can survive rather than how experienced they feel.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
           <t>---</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="3" t="inlineStr">
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
         <is>
           <t>Step 4.1. Two level ICP</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="4" t="inlineStr">
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
         <is>
           <t>---</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="3" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
         <is>
           <t>Which one to win first</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="4" t="inlineStr">
-        <is>
-          <t>**Level 2, and this is a change of emphasis worth stating plainly.**</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>The skill's instinct, and most GTM instinct, is to start at Level 1 because it is the larger and more visible group. Three findings in this run point the other way.</t>
+          <t>**Level 2, and the band framing makes the reason sharper than it was.**</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>• Level 2 has a live deal. Phase 1 put both quadrant 1 services on work applied</t>
+          <t>The skill's instinct, and most GTM instinct, is to start at Level 1 because it is the larger and more visible group. Three findings in this run point the other way.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>to the member's own deal. A Level 1 member with no live deal cannot use the differentiated half of the offer, only the commodity half.</t>
+          <t>• Level 2 has a live deal. Phase 1 put both quadrant 1 services on work applied</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>• Level 2 survives the first fortnight. The strongest quantified finding in the</t>
+          <t>to the member's own deal. A Level 1 member with no live deal cannot use the differentiated half of the offer, only the commodity half.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>research is 30 to 50 percent churn in the first 14 days among members who never act and never post. A member with an active target market deal has something to post about on day two. A member without one does not.</t>
+          <t>• Level 2 survives the first fortnight. The strongest quantified finding in the</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>• Level 2 can pay. Level 1's income band is unknown and the payment rail</t>
+          <t>research is 30 to 50 percent churn in the first 14 days among members who never act and never post. A member with an active target market deal has something to post about on day two. A member without one does not.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>constraints in `00-RESEARCH-FINDINGS.md` bite hardest at the low end. Someone already receiving target market income has a working rail and a reference point for the price.</t>
+          <t>• Level 2 can pay. Level 1's income band is unknown and the payment rail</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>Level 1 is still the larger audience and the correct target for the top of funnel. The scorecard, the organic content, and the buyer's checklist all speak to Level 1. The paid room is built for Level 2 first.</t>
+          <t>constraints in `00-RESEARCH-FINDINGS.md` bite hardest at the low end. Someone already receiving target market income has a working rail and a reference point for the price.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>That split is deliberate: acquire broad, admit narrow, and let the scorecard do the sorting.</t>
+          <t>Level 1 is still the larger audience and the correct target for the top of funnel. The scorecard, the organic content, and the buyer's checklist all speak to Level 1. The paid room is built for Level 2 first.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>---</t>
+          <t>That split is deliberate: acquire broad, admit narrow, and let the scorecard do the sorting.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>Payment rail split inside the ICP</t>
+          <t>What the band framing fixes</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>Not a field the skill asks for. It earns a row because it cuts the ICP in half along a line that has nothing to do with intent.</t>
+          <t>The previous version of this phase had a problem it did not name. Level 1 is the larger audience and the differentiated half of the offer was useless to them, because they had no live deal and no procurement to clear. That made Level 1 an audience to market to and not an audience to serve, which is a bad position to hold for long.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>Two of the five named markets can pay a monthly card charge without friction, two cannot reliably, and one is unresearched. This goes to Phase 9 as a packaging requirement and to Phase 7 stage 4 as a blocker.</t>
+          <t>The ladder resolves it. A band 1 member has somewhere to go and the first rungs are cheap: a W-8BEN on file, a scope that survives forwarding, an invoice that matches a vendor master record. None of that requires a large deal to be worth doing, and all of it is invisible in free content because free content is made by people who already cleared it.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
+          <t>**Level 2 still comes first for the paid room.** The difference is that Level 1 now has a curriculum rather than a waiting list.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
           <t>---</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="3" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>Payment rail split inside the ICP</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>Not a field the skill asks for. It earns a row because it cuts the ICP in half along a line that has nothing to do with intent.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>Two of the five named markets can pay a monthly card charge without friction, two cannot reliably, and one is unresearched. This goes to Phase 9 as a packaging requirement and to Phase 7 stage 4 as a blocker.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="inlineStr">
         <is>
           <t>Carried forward</t>
         </is>
@@ -670,7 +705,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C15"/>
+  <dimension ref="A1:C17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="62" customWidth="1" min="1" max="1"/>
@@ -824,83 +859,117 @@
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>Best engagement model</t>
+          <t>Band position</t>
         </is>
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>Self serve entry through the scorecard, then a low friction cohort or membership tier. Cannot yet justify a high ticket</t>
+          <t>Band 1, and usually unaware bands 2 to 4 exist. Selling where one person decides and no formal process runs. A band 2 opportunity would stall in their paperwork</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>Membership with the applied services attached. The one to one anchor tier is realistic here, not at Level 1</t>
+          <t>Band 1 to 2, trying to reach band 3. Has cleared a light process at least once, often without noticing, and cannot repeat it</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>Challenges and pain points</t>
+          <t>What blocks the next band</t>
         </is>
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>Cannot tell why a target market conversation goes quiet. No visibility of what the buyer checks. Prices against the wrong reference. No credibility artifacts a foreign buyer recognises. Payment and contracting friction. Isolated, nobody around them has done it</t>
+          <t>Nothing on file. No tax form, no contract template, no scope document that survives forwarding</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>Cannot repeat what worked. Priced too low at the start and cannot raise it on existing clients. Scope creeps. Wins on capability and loses on presentation against competitors who are worse and more legible. Dependent on one or two clients</t>
+          <t>Paperwork exists but is ad hoc. No security evidence at all. No insurance</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
         <is>
-          <t>Why they should choose us</t>
+          <t>Best engagement model</t>
         </is>
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>Because the thing they are missing is not skill, and every other option on the table sells skill. This is the only offer in the verified set built around one origin, one destination, and their own live deal</t>
+          <t>Self serve entry through the scorecard, then a low friction cohort or membership tier. Cannot yet justify a high ticket</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>Because the constraint has moved from access to consistency, and a room of people running the same motion plus review of their actual deals is what makes a motion repeatable</t>
+          <t>Membership with the applied services attached. The one to one anchor tier is realistic here, not at Level 1</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>Strategic goals</t>
+          <t>Challenges and pain points</t>
         </is>
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>Reach a buyer outside the local market. Stop competing on a list. Learn what good looks like from the buyer's side</t>
+          <t>Cannot tell why a target market conversation goes quiet. No visibility of what the buyer checks. Prices against the wrong reference. No credibility artifacts a foreign buyer recognises. Payment and contracting friction. Isolated, nobody around them has done it</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>Repeat it deliberately. Raise price at renewal. Replace marketplace dependence with a direct motion. Reduce client concentration</t>
+          <t>Cannot repeat what worked. Priced too low at the start and cannot raise it on existing clients. Scope creeps. Wins on capability and loses on presentation against competitors who are worse and more legible. Dependent on one or two clients</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
         <is>
+          <t>Why they should choose us</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>Because the thing they are missing is not skill, and every other option on the table sells skill. This is the only offer in the verified set built around one origin, one destination, and their own live deal</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>Because the constraint has moved from access to consistency, and a room of people running the same motion plus review of their actual deals is what makes a motion repeatable</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="6" t="inlineStr">
+        <is>
+          <t>Strategic goals</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="inlineStr">
+        <is>
+          <t>Reach a buyer outside the local market. Stop competing on a list. Learn what good looks like from the buyer's side</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>Repeat it deliberately. Raise price at renewal. Replace marketplace dependence with a direct motion. Reduce client concentration</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="6" t="inlineStr">
+        <is>
           <t>Triggers</t>
         </is>
       </c>
-      <c r="B15" s="6" t="inlineStr">
+      <c r="B17" s="6" t="inlineStr">
         <is>
           <t>Lost a target market deal without explanation. Watched a visibly weaker competitor win. Hit the local price ceiling. Currency or payment shock made local income feel unsafe. Finished a course and still had no buyer</t>
         </is>
       </c>
-      <c r="C15" s="6" t="inlineStr">
+      <c r="C17" s="6" t="inlineStr">
         <is>
           <t>Landed one target market client and cannot find a second. Client concentration got uncomfortable. Tried to raise rates and got refused. Scope on a fixed price deal ran away</t>
         </is>
@@ -1014,7 +1083,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B7"/>
+  <dimension ref="A1:B8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="61" customWidth="1" min="1" max="1"/>
@@ -1043,46 +1112,58 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>Level 2 first for the paid room, Level 1 for top of funnel</t>
+          <t>Band position per level</t>
         </is>
       </c>
       <c r="B4" s="6" t="inlineStr">
         <is>
-          <t>Phase 5, Phase 8, Phase 9</t>
+          <t>Phase 9 tiers, scorecard bands, curriculum sequencing</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
+          <t>Level 2 first for the paid room, Level 1 for top of funnel</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>Phase 5, Phase 8, Phase 9</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
           <t>Triggers, both levels</t>
         </is>
       </c>
-      <c r="B5" s="6" t="inlineStr">
+      <c r="B6" s="6" t="inlineStr">
         <is>
           <t>Phase 7 stage 1. Phase 6 copy drills. Scorecard questions</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="7" t="inlineStr">
+    <row r="7">
+      <c r="A7" s="7" t="inlineStr">
         <is>
           <t>Income band {TBD}</t>
         </is>
       </c>
-      <c r="B6" s="6" t="inlineStr">
+      <c r="B7" s="6" t="inlineStr">
         <is>
           <t>Scorecard question, design partner interviews</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="6" t="inlineStr">
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
         <is>
           <t>Payment rail split</t>
         </is>
       </c>
-      <c r="B7" s="6" t="inlineStr">
+      <c r="B8" s="6" t="inlineStr">
         <is>
           <t>Phase 7 stage 4, Phase 9 Step 9.2</t>
         </is>
